--- a/data/trans_bre/P0901-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,65</t>
+          <t>1,35; 8,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,94</t>
+          <t>4,93; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 14,71</t>
+          <t>5,76; 14,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 9,11</t>
+          <t>1,68; 8,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,74; 114,59</t>
+          <t>12,28; 117,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,01; 118,25</t>
+          <t>32,68; 114,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,2; 133,15</t>
+          <t>38,46; 130,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,8; 71,7</t>
+          <t>8,74; 67,43</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,38</t>
+          <t>3,42; 9,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 13,31</t>
+          <t>6,32; 13,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,28</t>
+          <t>4,77; 11,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 16,16</t>
+          <t>7,03; 16,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 107,76</t>
+          <t>28,61; 111,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,01; 121,51</t>
+          <t>44,07; 123,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,91; 136,44</t>
+          <t>42,94; 133,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,26; 308,34</t>
+          <t>54,42; 284,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 12,78</t>
+          <t>5,19; 12,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,55</t>
+          <t>5,04; 12,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 13,7</t>
+          <t>6,66; 13,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 5,33</t>
+          <t>-9,53; 5,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,69; 189,49</t>
+          <t>48,85; 171,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,03; 150,78</t>
+          <t>43,2; 150,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,19; 190,2</t>
+          <t>64,4; 199,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,29; 37,25</t>
+          <t>-54,8; 34,9</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,98</t>
+          <t>6,03; 11,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,97</t>
+          <t>4,45; 11,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,54</t>
+          <t>5,0; 11,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,04</t>
+          <t>2,2; 10,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,25; 150,52</t>
+          <t>57,82; 151,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,27; 99,19</t>
+          <t>30,35; 101,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,26; 120,96</t>
+          <t>38,69; 124,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 79,42</t>
+          <t>15,03; 82,69</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,85</t>
+          <t>5,77; 8,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,66</t>
+          <t>6,92; 10,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,65</t>
+          <t>7,23; 10,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,29</t>
+          <t>2,96; 9,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,89; 105,6</t>
+          <t>59,29; 107,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,3; 97,22</t>
+          <t>53,74; 96,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,67; 109,19</t>
+          <t>64,43; 107,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,22; 86,49</t>
+          <t>22,56; 88,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0901-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,02</t>
+          <t>1,29; 7,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,15</t>
+          <t>5,01; 12,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 14,66</t>
+          <t>6,14; 14,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 8,94</t>
+          <t>1,7; 8,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 117,68</t>
+          <t>14,18; 114,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,68; 114,48</t>
+          <t>33,32; 117,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,46; 130,75</t>
+          <t>41,03; 132,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 67,43</t>
+          <t>9,68; 65,07</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,58</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>109,42%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,58</t>
+          <t>3,35; 9,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,41</t>
+          <t>5,98; 13,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,24</t>
+          <t>4,7; 10,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 16,48</t>
+          <t>5,37; 11,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,61; 111,24</t>
+          <t>29,9; 112,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,07; 123,13</t>
+          <t>42,65; 118,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,94; 133,23</t>
+          <t>40,49; 124,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,42; 284,09</t>
+          <t>39,21; 109,4</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,74%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 12,5</t>
+          <t>5,19; 12,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,4</t>
+          <t>5,36; 12,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,65</t>
+          <t>6,97; 13,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 5,14</t>
+          <t>1,98; 9,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,85; 171,84</t>
+          <t>49,94; 173,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,2; 150,42</t>
+          <t>44,11; 156,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,4; 199,11</t>
+          <t>69,66; 201,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,8; 34,9</t>
+          <t>12,56; 74,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>8,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,94</t>
+          <t>5,9; 12,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,11</t>
+          <t>4,38; 11,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,73</t>
+          <t>4,63; 11,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,18</t>
+          <t>5,47; 11,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,82; 151,5</t>
+          <t>56,23; 156,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,35; 101,59</t>
+          <t>31,13; 107,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,69; 124,04</t>
+          <t>35,72; 121,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,03; 82,69</t>
+          <t>35,82; 97,11</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,97</t>
+          <t>5,71; 9,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,64</t>
+          <t>7,03; 10,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,61</t>
+          <t>7,12; 10,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,35</t>
+          <t>5,47; 8,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,29; 107,94</t>
+          <t>58,13; 109,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,74; 96,58</t>
+          <t>53,85; 94,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,43; 107,94</t>
+          <t>64,83; 110,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,56; 88,01</t>
+          <t>37,97; 68,44</t>
         </is>
       </c>
     </row>
